--- a/src/test/resources/TestData/TestData_ModuleAccount.xlsx
+++ b/src/test/resources/TestData/TestData_ModuleAccount.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="189">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -543,6 +543,54 @@
   <si>
     <t>2026-01-11 21:37:41</t>
   </si>
+  <si>
+    <t>2026-02-04 20:59:07</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:05</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:12</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:18</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:24</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:30</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:36</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:42</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:49</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:45:56</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:46:03</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:46:09</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:46:15</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:46:21</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:46:27</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:46:33</t>
+  </si>
 </sst>
 </file>
 
@@ -32130,7 +32178,7 @@
         <v>148</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K3" t="s" s="0">
         <v>151</v>
@@ -32178,7 +32226,7 @@
         <v>148</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>151</v>
@@ -32224,7 +32272,7 @@
         <v>148</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="K5" t="s" s="0">
         <v>151</v>
@@ -32270,7 +32318,7 @@
         <v>148</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K6" t="s" s="0">
         <v>151</v>
@@ -32316,7 +32364,7 @@
         <v>148</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="K7" t="s" s="0">
         <v>151</v>
@@ -32362,7 +32410,7 @@
         <v>148</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="K8" t="s" s="0">
         <v>151</v>
@@ -32408,7 +32456,7 @@
         <v>148</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="K9" t="s" s="0">
         <v>151</v>
@@ -32454,7 +32502,7 @@
         <v>148</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="K10" t="s" s="0">
         <v>151</v>
@@ -32500,7 +32548,7 @@
         <v>148</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="K11" t="s" s="0">
         <v>151</v>
@@ -32546,7 +32594,7 @@
         <v>148</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="K12" t="s" s="0">
         <v>151</v>
@@ -32592,7 +32640,7 @@
         <v>148</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="K13" t="s" s="0">
         <v>151</v>
@@ -32638,7 +32686,7 @@
         <v>148</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="K14" t="s" s="0">
         <v>151</v>
@@ -32684,7 +32732,7 @@
         <v>148</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="K15" t="s" s="0">
         <v>151</v>
@@ -32730,7 +32778,7 @@
         <v>148</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="K16" t="s" s="0">
         <v>151</v>
@@ -32776,7 +32824,7 @@
         <v>148</v>
       </c>
       <c r="J17" t="s" s="0">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="K17" t="s" s="0">
         <v>151</v>
